--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/02_WIM2 - Ön Analiz, Kaynak ve Çevreleme/EKG-KLT-FRM-39_garanti_arizasini_tekrar_olusturma_ve_test_sonuclari.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/02_WIM2 - Ön Analiz, Kaynak ve Çevreleme/EKG-KLT-FRM-39_garanti_arizasini_tekrar_olusturma_ve_test_sonuclari.xlsx
@@ -849,7 +849,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-39&amp;C&amp;"Arial,Regular"&amp;11Garanti Arızasını Tekrar Oluşturma ve Test Sonuçları</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Garanti tekrar test formu cam ürünlerine uyarlandı; kanıt, müşteri şartı ve atıflar düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -983,7 +984,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-39&amp;C&amp;"Arial,Regular"&amp;11Garanti Arızasını Tekrar Oluşturma ve Test Sonuçları</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Garanti tekrar test formu cam ürünlerine uyarlandı; kanıt, müşteri şartı ve atıflar düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>